--- a/important_mails_2026-03-29.xlsx
+++ b/important_mails_2026-03-29.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H160"/>
+  <dimension ref="A1:H155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3837,7 +3837,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3852,172 +3852,21 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Fri, 27 Feb 2026 08:54:27 +0000</t>
+          <t>Sat, 21 Mar 2026 06:12:01 +0000</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
+          <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
- DOC REVIEW</t>
+          <t>【爆单预警】百亿流量即将开闸！现在备货，抢占流量C位</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>Do not reply back to this e-mail!
-Hello,
-Thank you for submitting a document to the Chemical Safety Compliance Team.
-● The document uploaded for "B0FCDRNTT8" is incomplete, inaccurate or otherwise conflicting, and cannot be used for classification. Specifically:
-→ The SDS must be composed in accordance with a valid regulation/legislation for Chemical Safety Compliance( for which your product is listed and stored ).
-The SDS does not include the legislation/regulation in accordance with the document was created
-Legislation/regulation should be also mentioned in section 2 “Hazard Identification”.
-Once you have corrected the problems listed above, please re-upload a valid document in "Manage Your Compliance" on "Provide documents" section.
-For any questions/appeals regarding this product/other products, please submit them ( for each ASIN separately ) in "Manage Your Compliance" on the relevant Appeal reason:
-1. Go to the Performance tab and select Account health.
-2. Under Manage your compliance in the bottom right corner, click Product compliance requests.
-3. Click Add or appeal compliance button for the product you’re taking action on.
-4. To upload the documentation, drag and drop fil</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 27 Feb 2026 05:31:26 +0000</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai US,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
- For step-by-step instru</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 26 Feb 2026 21:23:05 +0000</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai CA,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
- For step-by-step instruct</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 21 Mar 2026 06:12:01 +0000</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>【爆单预警】百亿流量即将开闸！现在备货，抢占流量C位</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 						我们注意到您在店铺中有上架教育、办公类商品，特此预告您将有机会参与即将到来的全球教育采购 “超级旺季”！
@@ -4050,39 +3899,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 16:40:09 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -4098,39 +3947,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:16:22 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4146,39 +3995,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 10:25:38 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4196,39 +4045,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 09:02:06 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4245,39 +4094,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Tue, 17 Mar 2026 05:46:24 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>A Amazon enviou os itens vendidos</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  Processamos e enviamos seus pedidos do programa FBA - Logística da Amazon.
@@ -4301,39 +4150,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 14:55:03 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4348,39 +4197,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 11:03:39 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 45 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -4396,39 +4245,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:19:31 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 45 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -4445,40 +4294,40 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:50:00 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 45 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -4494,39 +4343,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 14:17:27 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace KSA &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>FBA removal fees will not apply in UAE and Saudi Arabia</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
 Amazon UAE
@@ -4546,39 +4395,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 11:10:46 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -4594,40 +4443,40 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 12:18:47 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
  Bands is still in your basket</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -4643,39 +4492,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 09:31:04 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>春季促销日 2026：最后提报您促销活动的机会</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -4692,39 +4541,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 15:38:05 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 2/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -4743,39 +4592,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 11:10:45 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -4793,39 +4642,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Sat, 7 Mar 2026 01:02:00 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 2/2026</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Credit Note for the month of 2/2026 is now available in your Seller Central Account.
@@ -4837,39 +4686,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:28:03 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4881,39 +4730,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:16:57 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -4925,39 +4774,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:10:12 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -4969,39 +4818,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 22:15:50 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5013,39 +4862,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 21:01:28 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Realizacja przez Amazon za 2 2026</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 2 i rok 2026.
@@ -5057,39 +4906,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:56:07 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5101,39 +4950,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5145,39 +4994,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:57 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -5195,39 +5044,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:26 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  尊敬的 Weihai EU：
@@ -5270,39 +5119,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:57 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -5319,40 +5168,40 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:27 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -5370,39 +5219,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:12:48 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -5420,39 +5269,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:07:18 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5464,39 +5313,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:17 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5508,39 +5357,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:06 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 2/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5559,39 +5408,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:35:00 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5603,39 +5452,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:32:44 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5647,39 +5496,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:24:20 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5691,39 +5540,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:55:05 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5735,39 +5584,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:24:37 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5779,39 +5628,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:58:56 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5823,39 +5672,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:48:50 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5867,39 +5716,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:11:22 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5911,39 +5760,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:54:03 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5955,40 +5804,40 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:44:53 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 2/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -6007,39 +5856,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:38:12 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -6051,40 +5900,40 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:28:10 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>La tua Fattura Elettronica Amazon Marketing Service Amazon.it per
  2/2026</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Gentile Shen zhen shi wei hai zhong xin ke ji you xian,
 Ti informiamo che la tua Fattura Elettronica Amazon Marketing Service per il mese di 2/2026 è ora disponibile sul tuo account di Seller Central.
@@ -6096,39 +5945,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:09:11 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6140,39 +5989,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 15:32:33 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Fulfillment by Amazon Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) لتاجر Fulfilment by Amazon الخاصة بك لشهر 2/2026)</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6191,39 +6040,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 15:13:19 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6235,39 +6084,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 14:56:47 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 2/2026)</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6286,39 +6135,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 14:29:22 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Sprzedawcy za 2 2026</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Sprzedawcy za miesiąc 2 i rok 2026.
@@ -6330,39 +6179,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 11:10:20 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6378,40 +6227,40 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:11:42 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -6429,39 +6278,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:08:11 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -6479,39 +6328,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:32 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Spełnij wymogi zgodności dotyczące Twoich ofert</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
 Wymagane działanie: Ważna informacja dotycząca Twoich ofert produktów
@@ -6527,39 +6376,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:29 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Aborda los requisitos de cumplimiento de tus listings</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
 Toma medidas: Información importante sobre tus listings de producto
@@ -6577,39 +6426,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:16:47 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
  尊敬的 Weihai EU：
@@ -6650,39 +6499,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:16:22 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -6700,40 +6549,40 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:12:51 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -6751,39 +6600,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:11:28 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -6800,39 +6649,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:09:31 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -6850,39 +6699,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 11:10:25 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -6900,39 +6749,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 00:58:56 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>最后机会：请在3月9日前提报春季促销日的促销</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>3月9日前提报春季促销日促销
 尊敬的卖家，
@@ -6947,39 +6796,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Mon, 2 Mar 2026 21:40:34 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -6993,39 +6842,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 11:10:30 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -7041,39 +6890,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:13:10 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 60 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -7089,39 +6938,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:09:55 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 60 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -7138,40 +6987,40 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:07:47 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 60 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -7187,39 +7036,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Feb 2026 18:30:15 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para marzo</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para marzo
@@ -7248,39 +7097,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-02</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7301,39 +7150,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7357,39 +7206,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7412,39 +7261,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:45:45 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7467,39 +7316,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:21:22 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-26</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7521,39 +7370,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:58:29 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7576,39 +7425,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:29:25 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7631,39 +7480,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Tue, 3 Mar 2026 07:49:31 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>New removal fees for KSA apply starting March 30</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
  Effective March 30, 2026, removal fees will apply in the Kingdom of Saudi Arabia (KSA) for removals you initiate.
@@ -7689,149 +7538,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 27 Feb 2026 13:57:30 +0000</t>
-        </is>
-      </c>
-      <c r="E147" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F147" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-03-12</t>
-        </is>
-      </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated removals of unfulfillable inventory
- Required removals: First notification
- Required removals: First notification
- Hello,
-Your FBA inventory listed below became unsellable in the past seven days. You must create a removal order by 2026-03-12 or these items will be disposed of. Removal fees will apply. Review the affected items and next steps below.
-Unsellable products:
-- FNSKU: X00265F4H9 Quantity: 1
-- FNSKU: X002C17O8J Quantity: 1
- Why is this happening?
-This action is required because these items are no longer in sellable condition in our fulfilment centres. According to our FBA Required Removals policy, all unsuitable units must be removed within 14 days of notification. To learn more, go to our FBA Required Removals policy .
-We leveraged a combination of automated means to identify this issue and make this decision.
- How do I address this?
-Follow these steps to manage your unsellable inventory:
-- Check your complete list and quantity of unsellable items in the Manage FBA inventory .
-- Create a removal order (removal fees apply) by following the instructions in Remove inventory overview .
- To avoid future manual inventory removal orders, set up Automated Unfulfillab</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 27 Feb 2026 12:08:33 +0000</t>
-        </is>
-      </c>
-      <c r="E148" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F148" s="2" t="inlineStr">
-        <is>
-          <t>Disposal order created for unsellable FBA inventory</t>
-        </is>
-      </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated Removals of Unfulfillable Inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Hello,
-You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
- Why is this happening?
-This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
- Removal order ID:
-- uih6sNeVfd
- Unsellable Products:
-- FNSKU: B0DRCF83VZ Quantity: 2
-- FNSKU: X002A05YW5 Quantity: 1
- For more information about the disposal order process, see Remove inventory from a fulfilment centre .
- To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
- The Fulfilment by Amazon Team
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferen</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Mar 2026 03:22:21 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -7847,40 +7586,40 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:33:36 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7899,40 +7638,40 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:34:06 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7950,39 +7689,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:09:21 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Envie os documentos de conformidade do produto para evitar a remoção da oferta</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
  Envie os documentos de conformidade do produto para evitar a remoção da oferta
@@ -7996,39 +7735,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 12:07:27 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Atenda aos requisitos de conformidade em ofertas</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
 Ação necessária: Informações importantes sobre suas ofertas
@@ -8046,39 +7785,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 12:42:53 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.nl&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Wijziging in geschiktheid voor opties voor premiumverzending</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
 Wijziging in geschiktheid voor opties voor premiumverzending
@@ -8095,39 +7834,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 12:16:06 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.se&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Behörighet att ändra alternativ för Premiumfrakt</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
 Behörighet att ändra alternativ för Premiumfrakt
@@ -8145,40 +7884,40 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 05:10:16 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Premium Shipping option eligibility suspended due to program
  requirement violation</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
 Premium Shipping option eligibility suspended due to program requirement violation
@@ -8197,39 +7936,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:12 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Notifications Amazon Seller Central (Ne pas répondre) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Répondez aux exigences de conformité pour vos mises en vente</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>96
 Action requise : informations importantes concernant vos offres
@@ -8245,39 +7984,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Sun, 1 Mar 2026 00:16:30 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>View your US Q1-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q1-2026
@@ -8307,40 +8046,40 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:10:48 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 60 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8359,40 +8098,40 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Feb 2026 02:06:07 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 60 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
